--- a/outputs/496-34.xlsx
+++ b/outputs/496-34.xlsx
@@ -56,13 +56,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,13 +95,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -162,56 +156,52 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -468,123 +458,131 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="16.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="12.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <v>44237.7732407407</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <v>44236.6072685185</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D4" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>44216.5656018519</v>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D5" s="8" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>44220.5649074074</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D6" s="8" t="n">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="F6" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
         <v>222</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>44216.5656018519</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D8" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="12"/>
+      <c r="D9" s="11"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F6:F7"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/outputs/496-34.xlsx
+++ b/outputs/496-34.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -59,7 +59,7 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm"/>
-    <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
@@ -156,7 +156,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -193,11 +193,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -500,52 +504,59 @@
       <c r="J2" s="10"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8"/>
-      <c r="F3" s="9"/>
+      <c r="A3" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>44236.6072685185</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>44236.6072685185</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>20</v>
+        <v>44216.5656018519</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>44216.5656018519</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>25</v>
+        <v>44220.5649074074</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>44220.5649074074</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>45</v>
+        <v>44216.5656018519</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>25</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>45</v>
@@ -555,11 +566,18 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="F7" s="9"/>
+      <c r="A7" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>44220.5656018519</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
@@ -571,18 +589,14 @@
       <c r="C8" s="7" t="n">
         <v>44216.5656018519</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="11" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="11"/>
+      <c r="D9" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F6:F7"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
